--- a/data/source/weekly/cs-en-us-030pct.xlsx
+++ b/data/source/weekly/cs-en-us-030pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>20</v>
@@ -899,7 +899,7 @@
         <v>20</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -908,7 +908,7 @@
         <v>20</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>20</v>
@@ -917,7 +917,7 @@
         <v>20</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L15" s="15">
         <v>-100</v>
@@ -933,82 +933,82 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
+        <v>4</v>
+      </c>
+      <c r="G16" s="14">
         <v>6</v>
       </c>
-      <c r="G16" s="14">
-        <v>5</v>
-      </c>
       <c r="H16" s="15">
-        <v>20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="14">
         <v>10</v>
       </c>
       <c r="J16" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K16" s="15">
-        <v>0</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="L16" s="15">
-        <v>-23.076923076923</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="M16" s="15">
-        <v>-47.368421052631</v>
+        <v>-60</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.566037735849</v>
+        <v>-91.803278688524</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="14">
-        <v>5</v>
+      <c r="C17" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D17" s="14">
         <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>150</v>
+        <v>-100</v>
       </c>
       <c r="F17" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G17" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H17" s="15">
-        <v>7.692307692307</v>
+        <v>20</v>
       </c>
       <c r="I17" s="14">
         <v>23</v>
       </c>
       <c r="J17" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K17" s="15">
-        <v>43.75</v>
+        <v>27.777777777777</v>
       </c>
       <c r="L17" s="15">
-        <v>9.523809523809</v>
+        <v>0</v>
       </c>
       <c r="M17" s="15">
-        <v>91.666666666666</v>
+        <v>53.333333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>-67.605633802816</v>
+        <v>-70.886075949367</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,13 +1016,13 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>200</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
         <v>5</v>
@@ -1034,22 +1034,22 @@
         <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J18" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K18" s="15">
-        <v>-16.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="L18" s="15">
-        <v>-16.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="M18" s="15">
-        <v>-16.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.327102803738</v>
+        <v>-95.121951219512</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F19" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G19" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H19" s="15">
-        <v>-24</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I19" s="14">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J19" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K19" s="15">
-        <v>-30.555555555555</v>
+        <v>-20.512820512820</v>
       </c>
       <c r="L19" s="15">
-        <v>-43.181818181818</v>
+        <v>-41.509433962264</v>
       </c>
       <c r="M19" s="15">
-        <v>212.5</v>
+        <v>138.461538461538</v>
       </c>
       <c r="N19" s="15">
-        <v>-46.808510638297</v>
+        <v>-40.384615384615</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,7 +1101,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
         <v>-100</v>
@@ -1110,28 +1110,28 @@
         <v>4</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H20" s="15">
-        <v>33.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="14">
         <v>4</v>
       </c>
       <c r="J20" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L20" s="15">
-        <v>-55.555555555555</v>
+        <v>-60</v>
       </c>
       <c r="M20" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.189189189189</v>
+        <v>-89.473684210526</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D21" s="17">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E21" s="18">
-        <v>18.181818181818</v>
+        <v>-50</v>
       </c>
       <c r="F21" s="17">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G21" s="17">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H21" s="18">
-        <v>-7.692307692307</v>
+        <v>-10</v>
       </c>
       <c r="I21" s="17">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="J21" s="17">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.219178082191</v>
+        <v>-14.942528735632</v>
       </c>
       <c r="L21" s="18">
-        <v>-30.208333333333</v>
+        <v>-35.087719298245</v>
       </c>
       <c r="M21" s="18">
-        <v>24.074074074074</v>
+        <v>2.777777777777</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.414698162729</v>
+        <v>-82.710280373831</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>3</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>3</v>
@@ -1213,7 +1213,7 @@
         <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1227,7 +1227,7 @@
         <v>20</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>1</v>
@@ -1236,7 +1236,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I23" s="14">
         <v>1</v>
@@ -1245,7 +1245,7 @@
         <v>20</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L23" s="15">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D24" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E24" s="15">
-        <v>-38.461538461538</v>
+        <v>55.555555555555</v>
       </c>
       <c r="F24" s="14">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G24" s="14">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H24" s="15">
-        <v>-8.510638297872</v>
+        <v>-8.888888888888</v>
       </c>
       <c r="I24" s="14">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="J24" s="14">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="K24" s="15">
-        <v>-15.151515151515</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L24" s="15">
-        <v>-35.632183908046</v>
+        <v>-31.372549019607</v>
       </c>
       <c r="M24" s="15">
-        <v>86.666666666666</v>
+        <v>118.75</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1309,16 +1309,16 @@
         <v>20</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F25" s="14">
+        <v>2</v>
+      </c>
+      <c r="G25" s="14">
         <v>4</v>
       </c>
-      <c r="G25" s="14">
-        <v>5</v>
-      </c>
       <c r="H25" s="15">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="I25" s="14">
         <v>4</v>
@@ -1330,13 +1330,13 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L25" s="15">
-        <v>-76.470588235294</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G26" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H26" s="15">
-        <v>57.894736842105</v>
+        <v>71.428571428571</v>
       </c>
       <c r="I26" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J26" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K26" s="15">
-        <v>29.032258064516</v>
+        <v>26.470588235294</v>
       </c>
       <c r="L26" s="15">
-        <v>81.818181818181</v>
+        <v>38.709677419354</v>
       </c>
       <c r="M26" s="15">
-        <v>-6.976744186046</v>
+        <v>-12.244897959183</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1391,7 +1391,7 @@
         <v>20</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
@@ -1400,7 +1400,7 @@
         <v>20</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I27" s="13" t="s">
         <v>20</v>
@@ -1415,10 +1415,10 @@
         <v>-100</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1432,7 +1432,7 @@
         <v>20</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>2</v>
@@ -1441,7 +1441,7 @@
         <v>20</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I28" s="14">
         <v>4</v>
@@ -1450,16 +1450,16 @@
         <v>20</v>
       </c>
       <c r="K28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L28" s="15">
         <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1473,16 +1473,16 @@
         <v>20</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
@@ -1514,16 +1514,16 @@
         <v>20</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1576,13 +1576,13 @@
         <v>-100</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>44</v>

--- a/data/source/weekly/cs-en-us-030pct.xlsx
+++ b/data/source/weekly/cs-en-us-030pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -901,8 +901,8 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="F15" s="14">
+        <v>1</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -910,8 +910,8 @@
       <c r="H15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I15" s="13" t="s">
-        <v>20</v>
+      <c r="I15" s="14">
+        <v>1</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>20</v>
@@ -920,13 +920,13 @@
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N15" s="15">
-        <v>-100</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -936,20 +936,20 @@
       <c r="C16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="14">
         <v>3</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F16" s="14">
-        <v>4</v>
       </c>
       <c r="G16" s="14">
         <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="14">
         <v>10</v>
@@ -964,51 +964,51 @@
         <v>-41.176470588235</v>
       </c>
       <c r="M16" s="15">
-        <v>-60</v>
+        <v>-65.517241379310</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.803278688524</v>
+        <v>-92.248062015503</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="14">
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-100</v>
+        <v>-25</v>
       </c>
       <c r="F17" s="14">
         <v>12</v>
       </c>
       <c r="G17" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H17" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J17" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K17" s="15">
-        <v>27.777777777777</v>
+        <v>22.727272727272</v>
       </c>
       <c r="L17" s="15">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="M17" s="15">
-        <v>53.333333333333</v>
+        <v>50</v>
       </c>
       <c r="N17" s="15">
-        <v>-70.886075949367</v>
+        <v>-69.662921348314</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1025,31 +1025,31 @@
         <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
         <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I18" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J18" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K18" s="15">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="L18" s="15">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="M18" s="15">
-        <v>-25</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.121951219512</v>
+        <v>-94.029850746268</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G19" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H19" s="15">
-        <v>-9.090909090909</v>
+        <v>-16</v>
       </c>
       <c r="I19" s="14">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="J19" s="14">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="K19" s="15">
-        <v>-20.512820512820</v>
+        <v>-17.021276595744</v>
       </c>
       <c r="L19" s="15">
-        <v>-41.509433962264</v>
+        <v>-32.758620689655</v>
       </c>
       <c r="M19" s="15">
-        <v>138.461538461538</v>
+        <v>129.411764705882</v>
       </c>
       <c r="N19" s="15">
-        <v>-40.384615384615</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>-33.333333333333</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K20" s="15">
-        <v>-50</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L20" s="15">
-        <v>-60</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="M20" s="15">
-        <v>-50</v>
+        <v>-37.5</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.473684210526</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>-50</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G21" s="17">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H21" s="18">
-        <v>-10</v>
+        <v>-16.071428571428</v>
       </c>
       <c r="I21" s="17">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="J21" s="17">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="K21" s="18">
-        <v>-14.942528735632</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L21" s="18">
-        <v>-35.087719298245</v>
+        <v>-28</v>
       </c>
       <c r="M21" s="18">
-        <v>2.777777777777</v>
+        <v>5.882352941176</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.710280373831</v>
+        <v>-81.092436974789</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="14">
         <v>3</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M22" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1251,7 +1251,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>11</v>
+      </c>
+      <c r="D24" s="14">
         <v>14</v>
       </c>
-      <c r="D24" s="14">
-        <v>9</v>
-      </c>
       <c r="E24" s="15">
-        <v>55.555555555555</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="F24" s="14">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G24" s="14">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H24" s="15">
-        <v>-8.888888888888</v>
+        <v>-15.686274509803</v>
       </c>
       <c r="I24" s="14">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="J24" s="14">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="K24" s="15">
-        <v>-6.666666666666</v>
+        <v>-11.235955056179</v>
       </c>
       <c r="L24" s="15">
-        <v>-31.372549019607</v>
+        <v>-28.181818181818</v>
       </c>
       <c r="M24" s="15">
-        <v>118.75</v>
+        <v>107.894736842105</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>21</v>
+      <c r="C25" s="14">
+        <v>2</v>
+      </c>
+      <c r="D25" s="14">
+        <v>7</v>
+      </c>
+      <c r="E25" s="15">
+        <v>-71.428571428571</v>
       </c>
       <c r="F25" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H25" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J25" s="14">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.333333333333</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="L25" s="15">
-        <v>-77.777777777777</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G26" s="14">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H26" s="15">
-        <v>71.428571428571</v>
+        <v>31.578947368421</v>
       </c>
       <c r="I26" s="14">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J26" s="14">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K26" s="15">
-        <v>26.470588235294</v>
+        <v>25</v>
       </c>
       <c r="L26" s="15">
-        <v>38.709677419354</v>
+        <v>31.578947368421</v>
       </c>
       <c r="M26" s="15">
-        <v>-12.244897959183</v>
+        <v>-15.254237288135</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1393,8 +1393,8 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="F27" s="14">
+        <v>1</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1402,17 +1402,17 @@
       <c r="H27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I27" s="13" t="s">
-        <v>20</v>
+      <c r="I27" s="14">
+        <v>1</v>
       </c>
       <c r="J27" s="14">
         <v>1</v>
       </c>
       <c r="K27" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="G28" s="14">
+        <v>1</v>
+      </c>
+      <c r="H28" s="15">
+        <v>0</v>
       </c>
       <c r="I28" s="14">
         <v>4</v>
       </c>
-      <c r="J28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K28" s="13" t="s">
-        <v>21</v>
+      <c r="J28" s="14">
+        <v>1</v>
+      </c>
+      <c r="K28" s="15">
+        <v>300</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-030pct.xlsx
+++ b/data/source/weekly/cs-en-us-030pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -892,82 +892,82 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>1</v>
       </c>
-      <c r="J15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>21</v>
+      <c r="J15" s="14">
+        <v>1</v>
+      </c>
+      <c r="K15" s="15">
+        <v>0</v>
       </c>
       <c r="L15" s="15">
         <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>-66.666666666666</v>
+        <v>-80</v>
       </c>
       <c r="N15" s="15">
-        <v>-90.909090909090</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="14">
+        <v>3</v>
+      </c>
+      <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>200</v>
       </c>
       <c r="F16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="14">
         <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J16" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K16" s="15">
-        <v>-23.076923076923</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L16" s="15">
-        <v>-41.176470588235</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="M16" s="15">
-        <v>-65.517241379310</v>
+        <v>-56.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.248062015503</v>
+        <v>-90.780141843971</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
         <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="F17" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G17" s="14">
         <v>12</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J17" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K17" s="15">
-        <v>22.727272727272</v>
+        <v>23.076923076923</v>
       </c>
       <c r="L17" s="15">
-        <v>12.5</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M17" s="15">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N17" s="15">
-        <v>-69.662921348314</v>
+        <v>-68</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,38 +1018,38 @@
       <c r="C18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-50</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
         <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I18" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J18" s="14">
         <v>10</v>
       </c>
       <c r="K18" s="15">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="L18" s="15">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="M18" s="15">
-        <v>-11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.029850746268</v>
+        <v>-93.706293706293</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="F19" s="14">
         <v>21</v>
       </c>
       <c r="G19" s="14">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H19" s="15">
-        <v>-16</v>
+        <v>5</v>
       </c>
       <c r="I19" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J19" s="14">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K19" s="15">
-        <v>-17.021276595744</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="L19" s="15">
-        <v>-32.758620689655</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M19" s="15">
-        <v>129.411764705882</v>
+        <v>110</v>
       </c>
       <c r="N19" s="15">
-        <v>-40</v>
+        <v>-40.845070422535</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1107,31 +1107,31 @@
         <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="14">
         <v>7</v>
       </c>
       <c r="H20" s="15">
+        <v>-71.428571428571</v>
+      </c>
+      <c r="I20" s="14">
+        <v>6</v>
+      </c>
+      <c r="J20" s="14">
+        <v>10</v>
+      </c>
+      <c r="K20" s="15">
+        <v>-40</v>
+      </c>
+      <c r="L20" s="15">
         <v>-57.142857142857</v>
       </c>
-      <c r="I20" s="14">
-        <v>5</v>
-      </c>
-      <c r="J20" s="14">
-        <v>9</v>
-      </c>
-      <c r="K20" s="15">
-        <v>-44.444444444444</v>
-      </c>
-      <c r="L20" s="15">
-        <v>-61.538461538461</v>
-      </c>
       <c r="M20" s="15">
-        <v>-37.5</v>
+        <v>-25</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.5</v>
+        <v>-86.956521739130</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>-6.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
         <v>47</v>
       </c>
       <c r="G21" s="17">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.071428571428</v>
+        <v>-9.615384615384</v>
       </c>
       <c r="I21" s="17">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="J21" s="17">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.764705882352</v>
+        <v>-9.649122807017</v>
       </c>
       <c r="L21" s="18">
-        <v>-28</v>
+        <v>-24.817518248175</v>
       </c>
       <c r="M21" s="18">
-        <v>5.882352941176</v>
+        <v>10.752688172043</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.092436974789</v>
+        <v>-80.268199233716</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
-      </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>300</v>
+        <v>5</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="14">
         <v>3</v>
       </c>
       <c r="K22" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L22" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,29 +1223,29 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="14">
-        <v>1</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="14">
+        <v>1</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-100</v>
       </c>
       <c r="I23" s="14">
         <v>1</v>
       </c>
-      <c r="J23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K23" s="13" t="s">
-        <v>21</v>
+      <c r="J23" s="14">
+        <v>1</v>
+      </c>
+      <c r="K23" s="15">
+        <v>0</v>
       </c>
       <c r="L23" s="15">
         <v>0</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D24" s="14">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>-21.428571428571</v>
+        <v>-62.5</v>
       </c>
       <c r="F24" s="14">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G24" s="14">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H24" s="15">
-        <v>-15.686274509803</v>
+        <v>-30</v>
       </c>
       <c r="I24" s="14">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J24" s="14">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="K24" s="15">
-        <v>-11.235955056179</v>
+        <v>-22.123893805309</v>
       </c>
       <c r="L24" s="15">
-        <v>-28.181818181818</v>
+        <v>-31.782945736434</v>
       </c>
       <c r="M24" s="15">
-        <v>107.894736842105</v>
+        <v>114.634146341463</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>-71.428571428571</v>
+        <v>-25</v>
       </c>
       <c r="F25" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G25" s="14">
+        <v>11</v>
+      </c>
+      <c r="H25" s="15">
+        <v>-54.545454545454</v>
+      </c>
+      <c r="I25" s="14">
         <v>9</v>
       </c>
-      <c r="H25" s="15">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="I25" s="14">
-        <v>6</v>
-      </c>
       <c r="J25" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K25" s="15">
-        <v>-53.846153846153</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="L25" s="15">
-        <v>-66.666666666666</v>
+        <v>-60.869565217391</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>16.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="F26" s="14">
+        <v>18</v>
+      </c>
+      <c r="G26" s="14">
         <v>25</v>
       </c>
-      <c r="G26" s="14">
-        <v>19</v>
-      </c>
       <c r="H26" s="15">
-        <v>31.578947368421</v>
+        <v>-28</v>
       </c>
       <c r="I26" s="14">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J26" s="14">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K26" s="15">
-        <v>25</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L26" s="15">
-        <v>31.578947368421</v>
+        <v>10.638297872340</v>
       </c>
       <c r="M26" s="15">
-        <v>-15.254237288135</v>
+        <v>-25.714285714285</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>1</v>
       </c>
       <c r="J27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L27" s="15">
         <v>-66.666666666666</v>
@@ -1428,20 +1428,20 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" s="14">
+        <v>1</v>
+      </c>
+      <c r="H28" s="15">
         <v>-100</v>
-      </c>
-      <c r="F28" s="14">
-        <v>1</v>
-      </c>
-      <c r="G28" s="14">
-        <v>1</v>
-      </c>
-      <c r="H28" s="15">
-        <v>0</v>
       </c>
       <c r="I28" s="14">
         <v>4</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1625,8 +1625,8 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-030pct.xlsx
+++ b/data/source/weekly/cs-en-us-030pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -926,48 +926,48 @@
         <v>-80</v>
       </c>
       <c r="N15" s="15">
-        <v>-91.666666666666</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>2</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F16" s="14">
         <v>3</v>
-      </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
-      <c r="E16" s="15">
-        <v>200</v>
-      </c>
-      <c r="F16" s="14">
-        <v>4</v>
       </c>
       <c r="G16" s="14">
         <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="14">
         <v>13</v>
       </c>
       <c r="J16" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K16" s="15">
-        <v>-7.142857142857</v>
+        <v>-18.75</v>
       </c>
       <c r="L16" s="15">
-        <v>-31.578947368421</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-56.666666666666</v>
+        <v>-58.064516129032</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.780141843971</v>
+        <v>-91.333333333333</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G17" s="14">
         <v>12</v>
       </c>
       <c r="H17" s="15">
-        <v>8.333333333333</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J17" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K17" s="15">
-        <v>23.076923076923</v>
+        <v>25</v>
       </c>
       <c r="L17" s="15">
-        <v>14.285714285714</v>
+        <v>9.375</v>
       </c>
       <c r="M17" s="15">
-        <v>60</v>
+        <v>52.173913043478</v>
       </c>
       <c r="N17" s="15">
-        <v>-68</v>
+        <v>-69.026548672566</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,13 +1016,13 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="E18" s="15">
+        <v>200</v>
       </c>
       <c r="F18" s="14">
         <v>6</v>
@@ -1034,22 +1034,22 @@
         <v>20</v>
       </c>
       <c r="I18" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J18" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K18" s="15">
-        <v>-10</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L18" s="15">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="M18" s="15">
-        <v>0</v>
+        <v>9.090909090909</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.706293706293</v>
+        <v>-92.052980132450</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,54 +1057,54 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>-60</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G19" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H19" s="15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J19" s="14">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K19" s="15">
-        <v>-19.230769230769</v>
+        <v>-18.644067796610</v>
       </c>
       <c r="L19" s="15">
-        <v>-33.333333333333</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="M19" s="15">
-        <v>110</v>
+        <v>108.695652173913</v>
       </c>
       <c r="N19" s="15">
-        <v>-40.845070422535</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
@@ -1119,19 +1119,19 @@
         <v>6</v>
       </c>
       <c r="J20" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K20" s="15">
-        <v>-40</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="L20" s="15">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="M20" s="15">
         <v>-25</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.956521739130</v>
+        <v>-88</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,45 +1142,45 @@
         <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="F21" s="17">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G21" s="17">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H21" s="18">
-        <v>-9.615384615384</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="I21" s="17">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="J21" s="17">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.649122807017</v>
+        <v>-9.448818897637</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.817518248175</v>
+        <v>-26.282051282051</v>
       </c>
       <c r="M21" s="18">
-        <v>10.752688172043</v>
+        <v>12.745098039215</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.268199233716</v>
+        <v>-79.537366548042</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1207,10 +1207,10 @@
         <v>66.666666666666</v>
       </c>
       <c r="L22" s="15">
+        <v>25</v>
+      </c>
+      <c r="M22" s="15">
         <v>66.666666666666</v>
-      </c>
-      <c r="M22" s="15">
-        <v>150</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,11 +1223,11 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>-62.5</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="F24" s="14">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G24" s="14">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H24" s="15">
-        <v>-30</v>
+        <v>-34.848484848484</v>
       </c>
       <c r="I24" s="14">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="J24" s="14">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="K24" s="15">
-        <v>-22.123893805309</v>
+        <v>-26.515151515151</v>
       </c>
       <c r="L24" s="15">
-        <v>-31.782945736434</v>
+        <v>-33.103448275862</v>
       </c>
       <c r="M24" s="15">
-        <v>114.634146341463</v>
+        <v>115.555555555556</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>-25</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="F25" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G25" s="14">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H25" s="15">
-        <v>-54.545454545454</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J25" s="14">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K25" s="15">
-        <v>-47.058823529411</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="L25" s="15">
-        <v>-60.869565217391</v>
+        <v>-60</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>-75</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F26" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G26" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H26" s="15">
-        <v>-28</v>
+        <v>-25</v>
       </c>
       <c r="I26" s="14">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J26" s="14">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="K26" s="15">
-        <v>8.333333333333</v>
+        <v>3.389830508474</v>
       </c>
       <c r="L26" s="15">
-        <v>10.638297872340</v>
+        <v>7.017543859649</v>
       </c>
       <c r="M26" s="15">
-        <v>-25.714285714285</v>
+        <v>-24.691358024691</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
@@ -1453,7 +1453,7 @@
         <v>300</v>
       </c>
       <c r="L28" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1560,11 +1560,11 @@
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <v>-100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-030pct.xlsx
+++ b/data/source/weekly/cs-en-us-030pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="14">
         <v>1</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="N15" s="15">
-        <v>-92.307692307692</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,7 +937,7 @@
         <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
         <v>-100</v>
@@ -946,28 +946,28 @@
         <v>3</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H16" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="I16" s="14">
         <v>13</v>
       </c>
       <c r="J16" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K16" s="15">
-        <v>-18.75</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="L16" s="15">
-        <v>-45.833333333333</v>
+        <v>-48</v>
       </c>
       <c r="M16" s="15">
-        <v>-58.064516129032</v>
+        <v>-62.857142857142</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.333333333333</v>
+        <v>-91.925465838509</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G17" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H17" s="15">
-        <v>-8.333333333333</v>
+        <v>6.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J17" s="14">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K17" s="15">
-        <v>25</v>
+        <v>21.212121212121</v>
       </c>
       <c r="L17" s="15">
-        <v>9.375</v>
+        <v>8.108108108108</v>
       </c>
       <c r="M17" s="15">
-        <v>52.173913043478</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N17" s="15">
-        <v>-69.026548672566</v>
+        <v>-68</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="I18" s="14">
+        <v>16</v>
+      </c>
+      <c r="J18" s="14">
         <v>12</v>
       </c>
-      <c r="J18" s="14">
-        <v>11</v>
-      </c>
       <c r="K18" s="15">
-        <v>9.090909090909</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>0</v>
+        <v>6.666666666666</v>
       </c>
       <c r="M18" s="15">
-        <v>9.090909090909</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.052980132450</v>
+        <v>-90.643274853801</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
         <v>23</v>
       </c>
       <c r="G19" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="I19" s="14">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J19" s="14">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K19" s="15">
-        <v>-18.644067796610</v>
+        <v>-16.923076923076</v>
       </c>
       <c r="L19" s="15">
-        <v>-30.434782608695</v>
+        <v>-29.870129870129</v>
       </c>
       <c r="M19" s="15">
-        <v>108.695652173913</v>
+        <v>107.692307692308</v>
       </c>
       <c r="N19" s="15">
-        <v>-36</v>
+        <v>-32.5</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,20 +1100,20 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>-71.428571428571</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="14">
         <v>6</v>
@@ -1125,13 +1125,13 @@
         <v>-45.454545454545</v>
       </c>
       <c r="L20" s="15">
-        <v>-62.5</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="M20" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-88</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
         <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>-7.692307692307</v>
+        <v>23.076923076923</v>
       </c>
       <c r="F21" s="17">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="G21" s="17">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H21" s="18">
-        <v>-14.814814814814</v>
+        <v>3.773584905660</v>
       </c>
       <c r="I21" s="17">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="J21" s="17">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.448818897637</v>
+        <v>-6.428571428571</v>
       </c>
       <c r="L21" s="18">
-        <v>-26.282051282051</v>
+        <v>-24.712643678160</v>
       </c>
       <c r="M21" s="18">
-        <v>12.745098039215</v>
+        <v>14.912280701754</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.537366548042</v>
+        <v>-78.802588996763</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>0</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>200</v>
       </c>
       <c r="I22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="L22" s="15">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M22" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>10</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E24" s="15">
-        <v>-47.368421052631</v>
+        <v>25</v>
       </c>
       <c r="F24" s="14">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G24" s="14">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H24" s="15">
-        <v>-34.848484848484</v>
+        <v>-40</v>
       </c>
       <c r="I24" s="14">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="J24" s="14">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="K24" s="15">
-        <v>-26.515151515151</v>
+        <v>-23.571428571428</v>
       </c>
       <c r="L24" s="15">
-        <v>-33.103448275862</v>
+        <v>-35.151515151515</v>
       </c>
       <c r="M24" s="15">
-        <v>115.555555555556</v>
+        <v>91.071428571428</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>1</v>
       </c>
       <c r="D25" s="14">
+        <v>3</v>
+      </c>
+      <c r="E25" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F25" s="14">
         <v>7</v>
       </c>
-      <c r="E25" s="15">
-        <v>-85.714285714285</v>
-      </c>
-      <c r="F25" s="14">
-        <v>6</v>
-      </c>
       <c r="G25" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H25" s="15">
         <v>-66.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J25" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K25" s="15">
-        <v>-58.333333333333</v>
+        <v>-59.259259259259</v>
       </c>
       <c r="L25" s="15">
-        <v>-60</v>
+        <v>-62.068965517241</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>6</v>
+      </c>
+      <c r="D26" s="14">
         <v>9</v>
       </c>
-      <c r="D26" s="14">
-        <v>11</v>
-      </c>
       <c r="E26" s="15">
-        <v>-18.181818181818</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G26" s="14">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H26" s="15">
-        <v>-25</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="I26" s="14">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="J26" s="14">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="K26" s="15">
-        <v>3.389830508474</v>
+        <v>-1.470588235294</v>
       </c>
       <c r="L26" s="15">
-        <v>7.017543859649</v>
+        <v>9.836065573770</v>
       </c>
       <c r="M26" s="15">
-        <v>-24.691358024691</v>
+        <v>-23.863636363636</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="14">
         <v>2</v>
       </c>
       <c r="K27" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1434,26 +1434,26 @@
       <c r="E28" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="13" t="s">
-        <v>20</v>
+      <c r="F28" s="14">
+        <v>1</v>
       </c>
       <c r="G28" s="14">
         <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" s="14">
         <v>1</v>
       </c>
       <c r="K28" s="15">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L28" s="15">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-030pct.xlsx
+++ b/data/source/weekly/cs-en-us-030pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -911,63 +911,63 @@
         <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="14">
         <v>1</v>
       </c>
       <c r="K15" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M15" s="15">
-        <v>-60</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N15" s="15">
-        <v>-85.714285714285</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J16" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K16" s="15">
-        <v>-23.529411764705</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="L16" s="15">
-        <v>-48</v>
+        <v>-51.724137931034</v>
       </c>
       <c r="M16" s="15">
-        <v>-62.857142857142</v>
+        <v>-64.102564102564</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.925465838509</v>
+        <v>-92.045454545454</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-37.5</v>
       </c>
       <c r="F17" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G17" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H17" s="15">
-        <v>6.666666666666</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="I17" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J17" s="14">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="K17" s="15">
-        <v>21.212121212121</v>
+        <v>9.756097560975</v>
       </c>
       <c r="L17" s="15">
-        <v>8.108108108108</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M17" s="15">
         <v>66.666666666666</v>
       </c>
       <c r="N17" s="15">
-        <v>-68</v>
+        <v>-67.391304347826</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,13 +1016,13 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>300</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
         <v>9</v>
@@ -1034,22 +1034,22 @@
         <v>125</v>
       </c>
       <c r="I18" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J18" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K18" s="15">
-        <v>33.333333333333</v>
+        <v>21.428571428571</v>
       </c>
       <c r="L18" s="15">
-        <v>6.666666666666</v>
+        <v>13.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>14.285714285714</v>
+        <v>21.428571428571</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.643274853801</v>
+        <v>-90.710382513661</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F19" s="14">
+        <v>18</v>
+      </c>
+      <c r="G19" s="14">
         <v>23</v>
       </c>
-      <c r="G19" s="14">
-        <v>26</v>
-      </c>
       <c r="H19" s="15">
-        <v>-11.538461538461</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="I19" s="14">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J19" s="14">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="K19" s="15">
-        <v>-16.923076923076</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="L19" s="15">
-        <v>-29.870129870129</v>
+        <v>-31.764705882352</v>
       </c>
       <c r="M19" s="15">
-        <v>107.692307692308</v>
+        <v>100</v>
       </c>
       <c r="N19" s="15">
-        <v>-32.5</v>
+        <v>-28.395061728395</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="14">
+        <v>4</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H20" s="15">
-        <v>-33.333333333333</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I20" s="14">
         <v>6</v>
       </c>
       <c r="J20" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K20" s="15">
-        <v>-45.454545454545</v>
+        <v>-60</v>
       </c>
       <c r="L20" s="15">
         <v>-64.705882352941</v>
       </c>
       <c r="M20" s="15">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.888888888888</v>
+        <v>-90.163934426229</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>23.076923076923</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F21" s="17">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G21" s="17">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="H21" s="18">
-        <v>3.773584905660</v>
+        <v>-11.864406779661</v>
       </c>
       <c r="I21" s="17">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J21" s="17">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.428571428571</v>
+        <v>-11.180124223602</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.712643678160</v>
+        <v>-25.130890052356</v>
       </c>
       <c r="M21" s="18">
-        <v>14.912280701754</v>
+        <v>12.598425196850</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.802588996763</v>
+        <v>-78.560719640179</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1192,25 +1192,25 @@
         <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L22" s="15">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="M22" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>10</v>
       </c>
       <c r="D24" s="14">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E24" s="15">
-        <v>25</v>
+        <v>-37.5</v>
       </c>
       <c r="F24" s="14">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G24" s="14">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H24" s="15">
-        <v>-40</v>
+        <v>-44.776119402985</v>
       </c>
       <c r="I24" s="14">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="J24" s="14">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="K24" s="15">
-        <v>-23.571428571428</v>
+        <v>-25.641025641025</v>
       </c>
       <c r="L24" s="15">
-        <v>-35.151515151515</v>
+        <v>-34.831460674157</v>
       </c>
       <c r="M24" s="15">
-        <v>91.071428571428</v>
+        <v>84.126984126984</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
         <v>7</v>
       </c>
       <c r="G25" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H25" s="15">
-        <v>-66.666666666666</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="I25" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J25" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K25" s="15">
-        <v>-59.259259259259</v>
+        <v>-58.064516129032</v>
       </c>
       <c r="L25" s="15">
-        <v>-62.068965517241</v>
+        <v>-60.606060606060</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G26" s="14">
         <v>34</v>
       </c>
       <c r="H26" s="15">
-        <v>-29.411764705882</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="I26" s="14">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J26" s="14">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="K26" s="15">
-        <v>-1.470588235294</v>
+        <v>-1.351351351351</v>
       </c>
       <c r="L26" s="15">
-        <v>9.836065573770</v>
+        <v>15.873015873015</v>
       </c>
       <c r="M26" s="15">
-        <v>-23.863636363636</v>
+        <v>-25.510204081632</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="15">
         <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
         <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K28" s="15">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="L28" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1575,8 +1575,8 @@
       <c r="K31" s="15">
         <v>-100</v>
       </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+      <c r="L31" s="15">
+        <v>-100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-030pct.xlsx
+++ b/data/source/weekly/cs-en-us-030pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -904,11 +904,11 @@
       <c r="F15" s="14">
         <v>2</v>
       </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>100</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
         <v>3</v>
@@ -923,51 +923,51 @@
         <v>200</v>
       </c>
       <c r="M15" s="15">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="N15" s="15">
-        <v>-80</v>
+        <v>-82.352941176470</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>4</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="14">
-        <v>2</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F16" s="14">
-        <v>4</v>
-      </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>-33.333333333333</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="I16" s="14">
         <v>14</v>
       </c>
       <c r="J16" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K16" s="15">
-        <v>-26.315789473684</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="L16" s="15">
-        <v>-51.724137931034</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-64.102564102564</v>
+        <v>-65.853658536585</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.045454545454</v>
+        <v>-92.513368983957</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-37.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G17" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H17" s="15">
-        <v>-5.263157894736</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="I17" s="14">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J17" s="14">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K17" s="15">
-        <v>9.756097560975</v>
+        <v>4.255319148936</v>
       </c>
       <c r="L17" s="15">
-        <v>7.142857142857</v>
+        <v>11.363636363636</v>
       </c>
       <c r="M17" s="15">
-        <v>66.666666666666</v>
+        <v>63.333333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>-67.391304347826</v>
+        <v>-69.938650306748</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
         <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>125</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I18" s="14">
         <v>17</v>
       </c>
       <c r="J18" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K18" s="15">
-        <v>21.428571428571</v>
+        <v>6.25</v>
       </c>
       <c r="L18" s="15">
-        <v>13.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M18" s="15">
-        <v>21.428571428571</v>
+        <v>6.25</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.710382513661</v>
+        <v>-91.145833333333</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G19" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H19" s="15">
-        <v>-21.739130434782</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="I19" s="14">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J19" s="14">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="K19" s="15">
-        <v>-17.142857142857</v>
+        <v>-18.987341772151</v>
       </c>
       <c r="L19" s="15">
-        <v>-31.764705882352</v>
+        <v>-26.436781609195</v>
       </c>
       <c r="M19" s="15">
-        <v>100</v>
+        <v>93.939393939393</v>
       </c>
       <c r="N19" s="15">
-        <v>-28.395061728395</v>
+        <v>-24.705882352941</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
         <v>1</v>
       </c>
       <c r="G20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="I20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J20" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K20" s="15">
-        <v>-60</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="L20" s="15">
-        <v>-64.705882352941</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="M20" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.163934426229</v>
+        <v>-89.855072463768</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,75 +1139,75 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E21" s="18">
-        <v>-42.857142857142</v>
+        <v>-52.173913043478</v>
       </c>
       <c r="F21" s="17">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G21" s="17">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.864406779661</v>
+        <v>-27.142857142857</v>
       </c>
       <c r="I21" s="17">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="J21" s="17">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.180124223602</v>
+        <v>-16.304347826087</v>
       </c>
       <c r="L21" s="18">
-        <v>-25.130890052356</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M21" s="18">
-        <v>12.598425196850</v>
+        <v>7.692307692307</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.560719640179</v>
+        <v>-78.787878787878</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
         <v>7</v>
       </c>
       <c r="J22" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K22" s="15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>40</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M22" s="15">
         <v>133.333333333333</v>
@@ -1232,11 +1232,11 @@
       <c r="F23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="14">
-        <v>1</v>
-      </c>
-      <c r="H23" s="15">
-        <v>-100</v>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="14">
         <v>1</v>
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M23" s="15">
         <v>-50</v>
@@ -1265,34 +1265,34 @@
         <v>10</v>
       </c>
       <c r="D24" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>-37.5</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F24" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G24" s="14">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H24" s="15">
-        <v>-44.776119402985</v>
+        <v>-36.065573770491</v>
       </c>
       <c r="I24" s="14">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="J24" s="14">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="K24" s="15">
-        <v>-25.641025641025</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="L24" s="15">
-        <v>-34.831460674157</v>
+        <v>-33.684210526315</v>
       </c>
       <c r="M24" s="15">
-        <v>84.126984126984</v>
+        <v>70.270270270270</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1312,25 +1312,25 @@
         <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G25" s="14">
         <v>18</v>
       </c>
       <c r="H25" s="15">
-        <v>-61.111111111111</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J25" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K25" s="15">
-        <v>-58.064516129032</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L25" s="15">
-        <v>-60.606060606060</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G26" s="14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H26" s="15">
-        <v>-32.352941176470</v>
+        <v>-22.857142857142</v>
       </c>
       <c r="I26" s="14">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J26" s="14">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="K26" s="15">
-        <v>-1.351351351351</v>
+        <v>-4.819277108433</v>
       </c>
       <c r="L26" s="15">
-        <v>15.873015873015</v>
+        <v>19.696969696969</v>
       </c>
       <c r="M26" s="15">
-        <v>-25.510204081632</v>
+        <v>-26.168224299065</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
         <v>3</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
         <v>2</v>
       </c>
-      <c r="E28" s="15">
-        <v>-50</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J28" s="14">
         <v>3</v>
       </c>
       <c r="K28" s="15">
-        <v>100</v>
+        <v>166.666666666667</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="14">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-030pct.xlsx
+++ b/data/source/weekly/cs-en-us-030pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,7 +902,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -911,22 +911,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="14">
         <v>1</v>
       </c>
       <c r="K15" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L15" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M15" s="15">
-        <v>-62.5</v>
+        <v>-50</v>
       </c>
       <c r="N15" s="15">
-        <v>-82.352941176470</v>
+        <v>-78.947368421052</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -936,20 +936,20 @@
       <c r="C16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="14">
-        <v>4</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-100</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
         <v>1</v>
       </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>-88.888888888888</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="I16" s="14">
         <v>14</v>
@@ -961,13 +961,13 @@
         <v>-39.130434782608</v>
       </c>
       <c r="L16" s="15">
-        <v>-53.333333333333</v>
+        <v>-56.25</v>
       </c>
       <c r="M16" s="15">
-        <v>-65.853658536585</v>
+        <v>-69.565217391304</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.513368983957</v>
+        <v>-92.929292929292</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,78 +978,78 @@
         <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="F17" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G17" s="14">
         <v>21</v>
       </c>
       <c r="H17" s="15">
-        <v>-19.047619047619</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="I17" s="14">
+        <v>54</v>
+      </c>
+      <c r="J17" s="14">
         <v>49</v>
       </c>
-      <c r="J17" s="14">
-        <v>47</v>
-      </c>
       <c r="K17" s="15">
-        <v>4.255319148936</v>
+        <v>10.204081632653</v>
       </c>
       <c r="L17" s="15">
-        <v>11.363636363636</v>
+        <v>22.727272727272</v>
       </c>
       <c r="M17" s="15">
-        <v>63.333333333333</v>
+        <v>58.823529411764</v>
       </c>
       <c r="N17" s="15">
-        <v>-69.938650306748</v>
+        <v>-69.662921348314</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="14">
+      <c r="C18" s="14">
         <v>2</v>
       </c>
-      <c r="E18" s="15">
-        <v>-100</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
         <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>33.333333333333</v>
+        <v>60</v>
       </c>
       <c r="I18" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J18" s="14">
         <v>16</v>
       </c>
       <c r="K18" s="15">
-        <v>6.25</v>
+        <v>25</v>
       </c>
       <c r="L18" s="15">
-        <v>0</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M18" s="15">
-        <v>6.25</v>
+        <v>5.263157894736</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.145833333333</v>
+        <v>-90.099009900990</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G19" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H19" s="15">
-        <v>-18.518518518518</v>
+        <v>-25</v>
       </c>
       <c r="I19" s="14">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J19" s="14">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K19" s="15">
-        <v>-18.987341772151</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="L19" s="15">
-        <v>-26.436781609195</v>
+        <v>-28.125</v>
       </c>
       <c r="M19" s="15">
-        <v>93.939393939393</v>
+        <v>91.666666666666</v>
       </c>
       <c r="N19" s="15">
-        <v>-24.705882352941</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="14">
-        <v>2</v>
-      </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
         <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>-85.714285714285</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I20" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J20" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K20" s="15">
-        <v>-58.823529411764</v>
+        <v>-50</v>
       </c>
       <c r="L20" s="15">
-        <v>-58.823529411764</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="M20" s="15">
-        <v>-50</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.855072463768</v>
+        <v>-87.671232876712</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>15</v>
+      </c>
+      <c r="D21" s="17">
         <v>11</v>
       </c>
-      <c r="D21" s="17">
-        <v>23</v>
-      </c>
       <c r="E21" s="18">
-        <v>-52.173913043478</v>
+        <v>36.363636363636</v>
       </c>
       <c r="F21" s="17">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G21" s="17">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H21" s="18">
-        <v>-27.142857142857</v>
+        <v>-19.117647058823</v>
       </c>
       <c r="I21" s="17">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="J21" s="17">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="K21" s="18">
-        <v>-16.304347826087</v>
+        <v>-12.820512820512</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.222222222222</v>
+        <v>-19.431279620853</v>
       </c>
       <c r="M21" s="18">
-        <v>7.692307692307</v>
+        <v>7.594936708860</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.787878787878</v>
+        <v>-78.092783505154</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
         <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="I22" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J22" s="14">
         <v>7</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L22" s="15">
-        <v>16.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>133.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E24" s="15">
-        <v>-44.444444444444</v>
+        <v>-45</v>
       </c>
       <c r="F24" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G24" s="14">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H24" s="15">
-        <v>-36.065573770491</v>
+        <v>-32.258064516129</v>
       </c>
       <c r="I24" s="14">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="J24" s="14">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="K24" s="15">
-        <v>-27.586206896551</v>
+        <v>-28.350515463917</v>
       </c>
       <c r="L24" s="15">
-        <v>-33.684210526315</v>
+        <v>-31.188118811881</v>
       </c>
       <c r="M24" s="15">
-        <v>70.270270270270</v>
+        <v>73.75</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="F25" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G25" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H25" s="15">
-        <v>-66.666666666666</v>
+        <v>-56.25</v>
       </c>
       <c r="I25" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J25" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K25" s="15">
-        <v>-57.142857142857</v>
+        <v>-57.5</v>
       </c>
       <c r="L25" s="15">
-        <v>-58.333333333333</v>
+        <v>-54.054054054054</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
         <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
         <v>27</v>
       </c>
       <c r="G26" s="14">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H26" s="15">
-        <v>-22.857142857142</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I26" s="14">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J26" s="14">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.819277108433</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="L26" s="15">
-        <v>19.696969696969</v>
+        <v>17.333333333333</v>
       </c>
       <c r="M26" s="15">
-        <v>-26.168224299065</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,22 +1394,22 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="14">
         <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L27" s="15">
         <v>0</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I28" s="14">
         <v>8</v>
       </c>
       <c r="J28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K28" s="15">
-        <v>166.666666666667</v>
+        <v>100</v>
       </c>
       <c r="L28" s="15">
         <v>14.285714285714</v>

--- a/data/source/weekly/cs-en-us-030pct.xlsx
+++ b/data/source/weekly/cs-en-us-030pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -911,63 +911,63 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
         <v>1</v>
       </c>
       <c r="K15" s="15">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M15" s="15">
-        <v>-50</v>
+        <v>-37.5</v>
       </c>
       <c r="N15" s="15">
-        <v>-78.947368421052</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="14">
         <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>-85.714285714285</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I16" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J16" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K16" s="15">
-        <v>-39.130434782608</v>
+        <v>-37.5</v>
       </c>
       <c r="L16" s="15">
-        <v>-56.25</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="M16" s="15">
-        <v>-69.565217391304</v>
+        <v>-70.588235294117</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.929292929292</v>
+        <v>-92.857142857142</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>5</v>
+      </c>
+      <c r="D17" s="14">
         <v>4</v>
       </c>
-      <c r="D17" s="14">
-        <v>2</v>
-      </c>
       <c r="E17" s="15">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="F17" s="14">
         <v>19</v>
       </c>
       <c r="G17" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H17" s="15">
-        <v>-9.523809523809</v>
+        <v>-5</v>
       </c>
       <c r="I17" s="14">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="J17" s="14">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K17" s="15">
-        <v>10.204081632653</v>
+        <v>11.320754716981</v>
       </c>
       <c r="L17" s="15">
-        <v>22.727272727272</v>
+        <v>11.320754716981</v>
       </c>
       <c r="M17" s="15">
-        <v>58.823529411764</v>
+        <v>51.282051282051</v>
       </c>
       <c r="N17" s="15">
-        <v>-69.662921348314</v>
+        <v>-68.108108108108</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,7 +1016,7 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>20</v>
@@ -1025,31 +1025,31 @@
         <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="I18" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J18" s="14">
         <v>16</v>
       </c>
       <c r="K18" s="15">
-        <v>25</v>
+        <v>31.25</v>
       </c>
       <c r="L18" s="15">
-        <v>11.111111111111</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="M18" s="15">
-        <v>5.263157894736</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.099009900990</v>
+        <v>-90.454545454545</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E19" s="15">
-        <v>-25</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G19" s="14">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H19" s="15">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="I19" s="14">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J19" s="14">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K19" s="15">
-        <v>-20.689655172413</v>
+        <v>-17.777777777777</v>
       </c>
       <c r="L19" s="15">
-        <v>-28.125</v>
+        <v>-28.846153846153</v>
       </c>
       <c r="M19" s="15">
-        <v>91.666666666666</v>
+        <v>80.487804878048</v>
       </c>
       <c r="N19" s="15">
-        <v>-25</v>
+        <v>-27.450980392156</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H20" s="15">
-        <v>-57.142857142857</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I20" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J20" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K20" s="15">
-        <v>-50</v>
+        <v>-45</v>
       </c>
       <c r="L20" s="15">
-        <v>-47.058823529411</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="M20" s="15">
-        <v>-35.714285714285</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.671232876712</v>
+        <v>-85.333333333333</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,45 +1142,45 @@
         <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E21" s="18">
-        <v>36.363636363636</v>
+        <v>50</v>
       </c>
       <c r="F21" s="17">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G21" s="17">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H21" s="18">
-        <v>-19.117647058823</v>
+        <v>-16.923076923076</v>
       </c>
       <c r="I21" s="17">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="J21" s="17">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="K21" s="18">
-        <v>-12.820512820512</v>
+        <v>-9.756097560975</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.431279620853</v>
+        <v>-21.610169491525</v>
       </c>
       <c r="M21" s="18">
-        <v>7.594936708860</v>
+        <v>2.209944751381</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.092783505154</v>
+        <v>-77.657004830917</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
+        <v>2</v>
+      </c>
+      <c r="G22" s="14">
         <v>3</v>
       </c>
-      <c r="G22" s="14">
-        <v>4</v>
-      </c>
       <c r="H22" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="14">
         <v>8</v>
@@ -1223,32 +1223,32 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+      <c r="G23" s="14">
+        <v>1</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-100</v>
       </c>
       <c r="I23" s="14">
         <v>1</v>
       </c>
       <c r="J23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L23" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M23" s="15">
         <v>-50</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D24" s="14">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E24" s="15">
-        <v>-45</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G24" s="14">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H24" s="15">
-        <v>-32.258064516129</v>
+        <v>-21.666666666666</v>
       </c>
       <c r="I24" s="14">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="J24" s="14">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="K24" s="15">
-        <v>-28.350515463917</v>
+        <v>-23.5</v>
       </c>
       <c r="L24" s="15">
-        <v>-31.188118811881</v>
+        <v>-27.830188679245</v>
       </c>
       <c r="M24" s="15">
-        <v>73.75</v>
+        <v>80</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
-        <v>2</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>-60</v>
+        <v>-100</v>
       </c>
       <c r="F25" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G25" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H25" s="15">
-        <v>-56.25</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="I25" s="14">
         <v>17</v>
       </c>
       <c r="J25" s="14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K25" s="15">
+        <v>-61.363636363636</v>
+      </c>
+      <c r="L25" s="15">
         <v>-57.5</v>
-      </c>
-      <c r="L25" s="15">
-        <v>-54.054054054054</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F26" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G26" s="14">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H26" s="15">
-        <v>-18.181818181818</v>
+        <v>-6.25</v>
       </c>
       <c r="I26" s="14">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="J26" s="14">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.347826086956</v>
+        <v>-3</v>
       </c>
       <c r="L26" s="15">
-        <v>17.333333333333</v>
+        <v>16.867469879518</v>
       </c>
       <c r="M26" s="15">
-        <v>-18.518518518518</v>
+        <v>-15.652173913043</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1403,16 +1403,16 @@
         <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="14">
         <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,14 +1425,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="14">
+      <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>4</v>
@@ -1444,16 +1444,16 @@
         <v>33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J28" s="14">
         <v>4</v>
       </c>
       <c r="K28" s="15">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="L28" s="15">
-        <v>14.285714285714</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-030pct.xlsx
+++ b/data/source/weekly/cs-en-us-030pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,7 +902,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -926,7 +926,7 @@
         <v>-37.5</v>
       </c>
       <c r="N15" s="15">
-        <v>-75</v>
+        <v>-76.190476190476</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -936,38 +936,38 @@
       <c r="C16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
-      <c r="E16" s="15">
-        <v>0</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
         <v>2</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>-71.428571428571</v>
+        <v>-60</v>
       </c>
       <c r="I16" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J16" s="14">
         <v>24</v>
       </c>
       <c r="K16" s="15">
-        <v>-37.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-54.545454545454</v>
+        <v>-58.974358974359</v>
       </c>
       <c r="M16" s="15">
-        <v>-70.588235294117</v>
+        <v>-70.909090909090</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.857142857142</v>
+        <v>-92.951541850220</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
-      </c>
-      <c r="D17" s="14">
-        <v>4</v>
-      </c>
-      <c r="E17" s="15">
-        <v>25</v>
+        <v>8</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G17" s="14">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H17" s="15">
-        <v>-5</v>
+        <v>83.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="J17" s="14">
         <v>53</v>
       </c>
       <c r="K17" s="15">
-        <v>11.320754716981</v>
+        <v>26.415094339622</v>
       </c>
       <c r="L17" s="15">
-        <v>11.320754716981</v>
+        <v>15.517241379310</v>
       </c>
       <c r="M17" s="15">
-        <v>51.282051282051</v>
+        <v>63.414634146341</v>
       </c>
       <c r="N17" s="15">
-        <v>-68.108108108108</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>2</v>
+      </c>
+      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="E18" s="15">
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H18" s="15">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="I18" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J18" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K18" s="15">
-        <v>31.25</v>
+        <v>35.294117647058</v>
       </c>
       <c r="L18" s="15">
-        <v>-8.695652173913</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="M18" s="15">
-        <v>-8.695652173913</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.454545454545</v>
+        <v>-90.212765957446</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>9</v>
+      </c>
+      <c r="D19" s="14">
         <v>5</v>
       </c>
-      <c r="D19" s="14">
-        <v>3</v>
-      </c>
       <c r="E19" s="15">
-        <v>66.666666666666</v>
+        <v>80</v>
       </c>
       <c r="F19" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G19" s="14">
         <v>25</v>
       </c>
       <c r="H19" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="J19" s="14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K19" s="15">
-        <v>-17.777777777777</v>
+        <v>-12.631578947368</v>
       </c>
       <c r="L19" s="15">
-        <v>-28.846153846153</v>
+        <v>-23.853211009174</v>
       </c>
       <c r="M19" s="15">
-        <v>80.487804878048</v>
+        <v>84.444444444444</v>
       </c>
       <c r="N19" s="15">
-        <v>-27.450980392156</v>
+        <v>-20.952380952381</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
         <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>-44.444444444444</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I20" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J20" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K20" s="15">
-        <v>-45</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="L20" s="15">
-        <v>-42.105263157894</v>
+        <v>-40</v>
       </c>
       <c r="M20" s="15">
-        <v>-35.294117647058</v>
+        <v>-40</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.333333333333</v>
+        <v>-85.185185185185</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E21" s="18">
-        <v>50</v>
+        <v>162.5</v>
       </c>
       <c r="F21" s="17">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="G21" s="17">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.923076923076</v>
+        <v>21.153846153846</v>
       </c>
       <c r="I21" s="17">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="J21" s="17">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.756097560975</v>
+        <v>-3.286384976525</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.610169491525</v>
+        <v>-19.53125</v>
       </c>
       <c r="M21" s="18">
-        <v>2.209944751381</v>
+        <v>5.641025641025</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.657004830917</v>
+        <v>-76.775648252536</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>0</v>
       </c>
       <c r="F22" s="14">
         <v>2</v>
@@ -1198,19 +1198,19 @@
         <v>-33.333333333333</v>
       </c>
       <c r="I22" s="14">
+        <v>9</v>
+      </c>
+      <c r="J22" s="14">
         <v>8</v>
       </c>
-      <c r="J22" s="14">
-        <v>7</v>
-      </c>
       <c r="K22" s="15">
-        <v>14.285714285714</v>
+        <v>12.5</v>
       </c>
       <c r="L22" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="M22" s="15">
-        <v>166.666666666667</v>
+        <v>200</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,11 +1223,11 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D24" s="14">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E24" s="15">
-        <v>133.333333333333</v>
+        <v>58.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G24" s="14">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H24" s="15">
-        <v>-21.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="J24" s="14">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="K24" s="15">
-        <v>-23.5</v>
+        <v>-18.867924528301</v>
       </c>
       <c r="L24" s="15">
-        <v>-27.830188679245</v>
+        <v>-21.818181818181</v>
       </c>
       <c r="M24" s="15">
-        <v>80</v>
+        <v>91.111111111111</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="14">
-        <v>4</v>
-      </c>
-      <c r="E25" s="15">
-        <v>-100</v>
+      <c r="C25" s="14">
+        <v>2</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F25" s="14">
         <v>6</v>
       </c>
       <c r="G25" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H25" s="15">
-        <v>-64.705882352941</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="I25" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J25" s="14">
         <v>44</v>
       </c>
       <c r="K25" s="15">
-        <v>-61.363636363636</v>
+        <v>-56.818181818181</v>
       </c>
       <c r="L25" s="15">
-        <v>-57.5</v>
+        <v>-56.818181818181</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E26" s="15">
-        <v>12.5</v>
+        <v>600</v>
       </c>
       <c r="F26" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G26" s="14">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H26" s="15">
-        <v>-6.25</v>
+        <v>14.814814814814</v>
       </c>
       <c r="I26" s="14">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="J26" s="14">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K26" s="15">
-        <v>-3</v>
+        <v>2.970297029702</v>
       </c>
       <c r="L26" s="15">
-        <v>16.867469879518</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M26" s="15">
-        <v>-15.652173913043</v>
+        <v>-15.447154471544</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,13 +1394,13 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
-      </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>200</v>
+        <v>2</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
         <v>5</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>3</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
+        <v>3</v>
+      </c>
+      <c r="G28" s="14">
         <v>4</v>
       </c>
-      <c r="G28" s="14">
-        <v>3</v>
-      </c>
       <c r="H28" s="15">
-        <v>33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="14">
         <v>9</v>
       </c>
       <c r="J28" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K28" s="15">
-        <v>125</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L28" s="15">
-        <v>28.571428571428</v>
+        <v>12.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1484,31 +1484,31 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="14">
+        <v>1</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-100</v>
+        <v>-97.297297297297</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1525,23 +1525,23 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-100</v>
+        <v>-97.222222222222</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-030pct.xlsx
+++ b/data/source/weekly/cs-en-us-030pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -895,29 +895,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="G15" s="14">
+        <v>2</v>
+      </c>
+      <c r="H15" s="15">
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>5</v>
       </c>
       <c r="J15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>400</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L15" s="15">
         <v>150</v>
@@ -926,7 +926,7 @@
         <v>-37.5</v>
       </c>
       <c r="N15" s="15">
-        <v>-76.190476190476</v>
+        <v>-77.272727272727</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>2</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="14">
+        <v>4</v>
+      </c>
+      <c r="G16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="14">
-        <v>2</v>
-      </c>
-      <c r="G16" s="14">
-        <v>5</v>
-      </c>
       <c r="H16" s="15">
-        <v>-60</v>
+        <v>300</v>
       </c>
       <c r="I16" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J16" s="14">
         <v>24</v>
       </c>
       <c r="K16" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="L16" s="15">
-        <v>-58.974358974359</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M16" s="15">
-        <v>-70.909090909090</v>
+        <v>-70.491803278688</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.951541850220</v>
+        <v>-92.468619246861</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,7 +975,7 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>20</v>
@@ -984,31 +984,31 @@
         <v>21</v>
       </c>
       <c r="F17" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G17" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H17" s="15">
-        <v>83.333333333333</v>
+        <v>233.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J17" s="14">
         <v>53</v>
       </c>
       <c r="K17" s="15">
-        <v>26.415094339622</v>
+        <v>32.075471698113</v>
       </c>
       <c r="L17" s="15">
-        <v>15.517241379310</v>
+        <v>14.754098360655</v>
       </c>
       <c r="M17" s="15">
-        <v>63.414634146341</v>
+        <v>59.090909090909</v>
       </c>
       <c r="N17" s="15">
-        <v>-66.666666666666</v>
+        <v>-68.181818181818</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>4</v>
+      </c>
+      <c r="D18" s="14">
         <v>2</v>
-      </c>
-      <c r="D18" s="14">
-        <v>1</v>
       </c>
       <c r="E18" s="15">
         <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
         <v>3</v>
       </c>
       <c r="H18" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I18" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J18" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K18" s="15">
-        <v>35.294117647058</v>
+        <v>42.105263157894</v>
       </c>
       <c r="L18" s="15">
-        <v>-11.538461538461</v>
+        <v>0</v>
       </c>
       <c r="M18" s="15">
-        <v>-4.166666666666</v>
+        <v>0</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.212765957446</v>
+        <v>-89.328063241106</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>80</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G19" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>13.043478260869</v>
       </c>
       <c r="I19" s="14">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="J19" s="14">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="K19" s="15">
-        <v>-12.631578947368</v>
+        <v>-12.745098039215</v>
       </c>
       <c r="L19" s="15">
-        <v>-23.853211009174</v>
+        <v>-23.275862068965</v>
       </c>
       <c r="M19" s="15">
-        <v>84.444444444444</v>
+        <v>97.777777777777</v>
       </c>
       <c r="N19" s="15">
-        <v>-20.952380952381</v>
+        <v>-18.348623853211</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>7</v>
+      </c>
+      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="14">
-        <v>2</v>
-      </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>600</v>
       </c>
       <c r="F20" s="14">
+        <v>12</v>
+      </c>
+      <c r="G20" s="14">
         <v>6</v>
       </c>
-      <c r="G20" s="14">
-        <v>7</v>
-      </c>
       <c r="H20" s="15">
-        <v>-14.285714285714</v>
+        <v>100</v>
       </c>
       <c r="I20" s="14">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J20" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K20" s="15">
-        <v>-45.454545454545</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="L20" s="15">
-        <v>-40</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="M20" s="15">
-        <v>-40</v>
+        <v>-5</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.185185185185</v>
+        <v>-78.409090909090</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D21" s="17">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>162.5</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="G21" s="17">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="H21" s="18">
-        <v>21.153846153846</v>
+        <v>78.048780487804</v>
       </c>
       <c r="I21" s="17">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="J21" s="17">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.286384976525</v>
+        <v>1.333333333333</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.53125</v>
+        <v>-16.176470588235</v>
       </c>
       <c r="M21" s="18">
-        <v>5.641025641025</v>
+        <v>10.144927536231</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.775648252536</v>
+        <v>-75.974710221285</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
+        <v>3</v>
+      </c>
+      <c r="G22" s="14">
         <v>1</v>
       </c>
-      <c r="E22" s="15">
-        <v>0</v>
-      </c>
-      <c r="F22" s="14">
-        <v>2</v>
-      </c>
-      <c r="G22" s="14">
-        <v>3</v>
-      </c>
       <c r="H22" s="15">
-        <v>-33.333333333333</v>
+        <v>200</v>
       </c>
       <c r="I22" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J22" s="14">
         <v>8</v>
       </c>
       <c r="K22" s="15">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="L22" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>200</v>
+        <v>233.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D24" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>58.333333333333</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="F24" s="14">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G24" s="14">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H24" s="15">
-        <v>0</v>
+        <v>5.454545454545</v>
       </c>
       <c r="I24" s="14">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="J24" s="14">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="K24" s="15">
-        <v>-18.867924528301</v>
+        <v>-18.340611353711</v>
       </c>
       <c r="L24" s="15">
-        <v>-21.818181818181</v>
+        <v>-17.982456140350</v>
       </c>
       <c r="M24" s="15">
-        <v>91.111111111111</v>
+        <v>90.816326530612</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1305,32 +1305,32 @@
       <c r="C25" s="14">
         <v>2</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>21</v>
+      <c r="D25" s="14">
+        <v>7</v>
+      </c>
+      <c r="E25" s="15">
+        <v>-71.428571428571</v>
       </c>
       <c r="F25" s="14">
         <v>6</v>
       </c>
       <c r="G25" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H25" s="15">
-        <v>-53.846153846153</v>
+        <v>-62.5</v>
       </c>
       <c r="I25" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J25" s="14">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="K25" s="15">
-        <v>-56.818181818181</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="L25" s="15">
-        <v>-56.818181818181</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>600</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F26" s="14">
         <v>31</v>
       </c>
       <c r="G26" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H26" s="15">
-        <v>14.814814814814</v>
+        <v>6.896551724137</v>
       </c>
       <c r="I26" s="14">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="J26" s="14">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="K26" s="15">
-        <v>2.970297029702</v>
+        <v>-2.678571428571</v>
       </c>
       <c r="L26" s="15">
-        <v>14.285714285714</v>
+        <v>13.541666666666</v>
       </c>
       <c r="M26" s="15">
-        <v>-15.447154471544</v>
+        <v>-19.852941176470</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="G27" s="14">
+        <v>2</v>
+      </c>
+      <c r="H27" s="15">
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>5</v>
       </c>
       <c r="J27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
         <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>-25</v>
+        <v>-80</v>
       </c>
       <c r="I28" s="14">
         <v>9</v>
       </c>
       <c r="J28" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K28" s="15">
-        <v>28.571428571428</v>
+        <v>12.5</v>
       </c>
       <c r="L28" s="15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1500,15 +1500,15 @@
         <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-97.297297297297</v>
+        <v>-97.368421052631</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-97.222222222222</v>
+        <v>-97.297297297297</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-030pct.xlsx
+++ b/data/source/weekly/cs-en-us-030pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -895,20 +895,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>2</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>5</v>
@@ -923,10 +923,10 @@
         <v>150</v>
       </c>
       <c r="M15" s="15">
-        <v>-37.5</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="N15" s="15">
-        <v>-77.272727272727</v>
+        <v>-78.260869565217</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
+        <v>3</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="14">
+        <v>5</v>
+      </c>
+      <c r="G16" s="14">
         <v>4</v>
       </c>
-      <c r="G16" s="14">
-        <v>1</v>
-      </c>
       <c r="H16" s="15">
-        <v>300</v>
+        <v>25</v>
       </c>
       <c r="I16" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J16" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K16" s="15">
-        <v>-25</v>
+        <v>-29.629629629629</v>
       </c>
       <c r="L16" s="15">
-        <v>-57.142857142857</v>
+        <v>-56.818181818181</v>
       </c>
       <c r="M16" s="15">
-        <v>-70.491803278688</v>
+        <v>-70.769230769230</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.468619246861</v>
+        <v>-92.338709677419</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -977,38 +977,38 @@
       <c r="C17" s="14">
         <v>3</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+      <c r="D17" s="14">
+        <v>3</v>
+      </c>
+      <c r="E17" s="15">
+        <v>0</v>
       </c>
       <c r="F17" s="14">
         <v>20</v>
       </c>
       <c r="G17" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H17" s="15">
-        <v>233.333333333333</v>
+        <v>185.714285714286</v>
       </c>
       <c r="I17" s="14">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J17" s="14">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K17" s="15">
-        <v>32.075471698113</v>
+        <v>32.142857142857</v>
       </c>
       <c r="L17" s="15">
-        <v>14.754098360655</v>
+        <v>13.846153846153</v>
       </c>
       <c r="M17" s="15">
-        <v>59.090909090909</v>
+        <v>64.444444444444</v>
       </c>
       <c r="N17" s="15">
-        <v>-68.181818181818</v>
+        <v>-68.376068376068</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0</v>
+      </c>
+      <c r="F18" s="14">
+        <v>8</v>
+      </c>
+      <c r="G18" s="14">
         <v>4</v>
       </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
-      <c r="E18" s="15">
+      <c r="H18" s="15">
         <v>100</v>
       </c>
-      <c r="F18" s="14">
-        <v>9</v>
-      </c>
-      <c r="G18" s="14">
-        <v>3</v>
-      </c>
-      <c r="H18" s="15">
-        <v>200</v>
-      </c>
       <c r="I18" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J18" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K18" s="15">
-        <v>42.105263157894</v>
+        <v>40</v>
       </c>
       <c r="L18" s="15">
-        <v>0</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="M18" s="15">
-        <v>0</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.328063241106</v>
+        <v>-89.393939393939</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>-14.285714285714</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G19" s="14">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H19" s="15">
-        <v>13.043478260869</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="I19" s="14">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J19" s="14">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="K19" s="15">
-        <v>-12.745098039215</v>
+        <v>-18.965517241379</v>
       </c>
       <c r="L19" s="15">
-        <v>-23.275862068965</v>
+        <v>-22.950819672131</v>
       </c>
       <c r="M19" s="15">
-        <v>97.777777777777</v>
+        <v>91.836734693877</v>
       </c>
       <c r="N19" s="15">
-        <v>-18.348623853211</v>
+        <v>-17.543859649122</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>600</v>
+        <v>-75</v>
       </c>
       <c r="F20" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G20" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I20" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J20" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K20" s="15">
-        <v>-17.391304347826</v>
+        <v>-25.925925925925</v>
       </c>
       <c r="L20" s="15">
-        <v>-13.636363636363</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M20" s="15">
-        <v>-5</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N20" s="15">
-        <v>-78.409090909090</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>83.333333333333</v>
+        <v>-56</v>
       </c>
       <c r="F21" s="17">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G21" s="17">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="H21" s="18">
-        <v>78.048780487804</v>
+        <v>27.272727272727</v>
       </c>
       <c r="I21" s="17">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="J21" s="17">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="K21" s="18">
-        <v>1.333333333333</v>
+        <v>-4</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.176470588235</v>
+        <v>-16.376306620209</v>
       </c>
       <c r="M21" s="18">
-        <v>10.144927536231</v>
+        <v>8.597285067873</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.974710221285</v>
+        <v>-76.071784646061</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I22" s="14">
         <v>10</v>
@@ -1265,34 +1265,34 @@
         <v>14</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E24" s="15">
-        <v>-17.647058823529</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="F24" s="14">
+        <v>60</v>
+      </c>
+      <c r="G24" s="14">
         <v>58</v>
       </c>
-      <c r="G24" s="14">
-        <v>55</v>
-      </c>
       <c r="H24" s="15">
-        <v>5.454545454545</v>
+        <v>3.448275862068</v>
       </c>
       <c r="I24" s="14">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="J24" s="14">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="K24" s="15">
-        <v>-18.340611353711</v>
+        <v>-21.031746031746</v>
       </c>
       <c r="L24" s="15">
-        <v>-17.982456140350</v>
+        <v>-14.957264957265</v>
       </c>
       <c r="M24" s="15">
-        <v>90.816326530612</v>
+        <v>91.346153846153</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>-71.428571428571</v>
+        <v>25</v>
       </c>
       <c r="F25" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G25" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H25" s="15">
-        <v>-62.5</v>
+        <v>-40</v>
       </c>
       <c r="I25" s="14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J25" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K25" s="15">
-        <v>-58.823529411764</v>
+        <v>-52.727272727272</v>
       </c>
       <c r="L25" s="15">
-        <v>-53.333333333333</v>
+        <v>-44.680851063829</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>4</v>
+      </c>
+      <c r="D26" s="14">
         <v>7</v>
       </c>
-      <c r="D26" s="14">
-        <v>11</v>
-      </c>
       <c r="E26" s="15">
-        <v>-36.363636363636</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F26" s="14">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G26" s="14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H26" s="15">
-        <v>6.896551724137</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="I26" s="14">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="J26" s="14">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.678571428571</v>
+        <v>-5.042016806722</v>
       </c>
       <c r="L26" s="15">
-        <v>13.541666666666</v>
+        <v>7.619047619047</v>
       </c>
       <c r="M26" s="15">
-        <v>-19.852941176470</v>
+        <v>-22.602739726027</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,28 +1388,28 @@
         <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
         <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="14">
         <v>5</v>
       </c>
       <c r="J27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L27" s="15">
         <v>0</v>
@@ -1428,20 +1428,20 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>1</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>-80</v>
+        <v>-75</v>
       </c>
       <c r="I28" s="14">
         <v>9</v>
@@ -1453,7 +1453,7 @@
         <v>12.5</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <v>1</v>
       </c>
       <c r="J29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L29" s="15">
         <v>-50</v>
@@ -1500,7 +1500,7 @@
         <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-97.368421052631</v>
+        <v>-97.435897435897</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>0</v>
       </c>
       <c r="I30" s="14">
         <v>1</v>
       </c>
       <c r="J30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L30" s="15">
         <v>-50</v>
@@ -1541,7 +1541,7 @@
         <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-97.297297297297</v>
+        <v>-97.368421052631</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-030pct.xlsx
+++ b/data/source/weekly/cs-en-us-030pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -901,14 +901,14 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14">
-        <v>1</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>5</v>
@@ -920,13 +920,13 @@
         <v>66.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M15" s="15">
         <v>-44.444444444444</v>
       </c>
       <c r="N15" s="15">
-        <v>-78.260869565217</v>
+        <v>-79.166666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
         <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>25</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J16" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K16" s="15">
-        <v>-29.629629629629</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="L16" s="15">
-        <v>-56.818181818181</v>
+        <v>-50</v>
       </c>
       <c r="M16" s="15">
-        <v>-70.769230769230</v>
+        <v>-69.014084507042</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.338709677419</v>
+        <v>-91.505791505791</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F17" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G17" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H17" s="15">
-        <v>185.714285714286</v>
+        <v>280</v>
       </c>
       <c r="I17" s="14">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J17" s="14">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K17" s="15">
-        <v>32.142857142857</v>
+        <v>36.206896551724</v>
       </c>
       <c r="L17" s="15">
-        <v>13.846153846153</v>
+        <v>12.857142857142</v>
       </c>
       <c r="M17" s="15">
-        <v>64.444444444444</v>
+        <v>64.583333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>-68.376068376068</v>
+        <v>-67.489711934156</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
         <v>100</v>
       </c>
       <c r="I18" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J18" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K18" s="15">
-        <v>40</v>
+        <v>47.619047619047</v>
       </c>
       <c r="L18" s="15">
-        <v>-6.666666666666</v>
+        <v>3.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-3.448275862068</v>
+        <v>3.333333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.393939393939</v>
+        <v>-88.727272727272</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E19" s="15">
-        <v>-64.285714285714</v>
+        <v>400</v>
       </c>
       <c r="F19" s="14">
         <v>25</v>
       </c>
       <c r="G19" s="14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H19" s="15">
-        <v>-13.793103448275</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="I19" s="14">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J19" s="14">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K19" s="15">
-        <v>-18.965517241379</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="L19" s="15">
-        <v>-22.950819672131</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M19" s="15">
-        <v>91.836734693877</v>
+        <v>98</v>
       </c>
       <c r="N19" s="15">
-        <v>-17.543859649122</v>
+        <v>-13.913043478260</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G20" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H20" s="15">
-        <v>22.222222222222</v>
+        <v>25</v>
       </c>
       <c r="I20" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J20" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K20" s="15">
-        <v>-25.925925925925</v>
+        <v>-25</v>
       </c>
       <c r="L20" s="15">
-        <v>-9.090909090909</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="M20" s="15">
-        <v>-9.090909090909</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="N20" s="15">
-        <v>-80</v>
+        <v>-79.807692307692</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E21" s="18">
-        <v>-56</v>
+        <v>112.5</v>
       </c>
       <c r="F21" s="17">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G21" s="17">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H21" s="18">
-        <v>27.272727272727</v>
+        <v>33.962264150943</v>
       </c>
       <c r="I21" s="17">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="J21" s="17">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="K21" s="18">
-        <v>-4</v>
+        <v>-0.387596899224</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.376306620209</v>
+        <v>-13.468013468013</v>
       </c>
       <c r="M21" s="18">
-        <v>8.597285067873</v>
+        <v>10.300429184549</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.071784646061</v>
+        <v>-75.35953978907</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I22" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J22" s="14">
         <v>8</v>
       </c>
       <c r="K22" s="15">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="L22" s="15">
-        <v>66.666666666666</v>
+        <v>83.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>233.333333333333</v>
+        <v>266.666666666667</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1232,11 +1232,11 @@
       <c r="F23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="14">
-        <v>1</v>
-      </c>
-      <c r="H23" s="15">
-        <v>-100</v>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="14">
         <v>1</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D24" s="14">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>-39.130434782608</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="F24" s="14">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G24" s="14">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="H24" s="15">
-        <v>3.448275862068</v>
+        <v>-14.084507042253</v>
       </c>
       <c r="I24" s="14">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="J24" s="14">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="K24" s="15">
-        <v>-21.031746031746</v>
+        <v>-21.033210332103</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.957264957265</v>
+        <v>-13.008130081300</v>
       </c>
       <c r="M24" s="15">
-        <v>91.346153846153</v>
+        <v>101.88679245283</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
         <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>25</v>
+        <v>-25</v>
       </c>
       <c r="F25" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G25" s="14">
         <v>15</v>
       </c>
       <c r="H25" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="I25" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J25" s="14">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K25" s="15">
-        <v>-52.727272727272</v>
+        <v>-50.847457627118</v>
       </c>
       <c r="L25" s="15">
-        <v>-44.680851063829</v>
+        <v>-39.583333333333</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>-42.857142857142</v>
+        <v>80</v>
       </c>
       <c r="F26" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G26" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H26" s="15">
-        <v>-3.703703703703</v>
+        <v>12.5</v>
       </c>
       <c r="I26" s="14">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="J26" s="14">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="K26" s="15">
-        <v>-5.042016806722</v>
+        <v>-0.806451612903</v>
       </c>
       <c r="L26" s="15">
-        <v>7.619047619047</v>
+        <v>10.810810810810</v>
       </c>
       <c r="M26" s="15">
-        <v>-22.602739726027</v>
+        <v>-23.125</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>1</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="14">
         <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
         <v>5</v>
@@ -1412,7 +1412,7 @@
         <v>-16.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
         <v>1</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-75</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>-25</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="14">
+      <c r="C29" s="14">
         <v>1</v>
       </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="14">
         <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
         <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-97.435897435897</v>
+        <v>-95</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="14">
+      <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
         <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M30" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>-97.368421052631</v>
+        <v>-94.871794871794</v>
       </c>
     </row>
     <row r="31" spans="1:14">
